--- a/Configs/GameConfig/Datas/unit.xlsx
+++ b/Configs/GameConfig/Datas/unit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>targetPolicy</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,165 +514,138 @@
           <t>string</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>状态标注(CORE_COMPLETE)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>索引</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>动画键</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>攻击距离(格)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>攻击力</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>攻击间隔(秒)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>伤害模式</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>目标策略</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="n">
+    <row r="6">
+      <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>刀</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>knife</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>单体</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>nearest</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CORE_COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>弓</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>bow</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>3.5</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>closest_end</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>枪</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>pike</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2.5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -680,33 +658,37 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>近战枪击</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nearest</t>
+          <t>closest_end</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CORE_COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>骑</t>
+          <t>枪</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cavalry</t>
+          <t>pike</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -719,12 +701,60 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>近战枪击</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CORE_COMPLETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>骑</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cavalry</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>范围</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>nearest</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CORE_COMPLETE</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/unit.xlsx
+++ b/Configs/GameConfig/Datas/unit.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28b018f849ce4a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63b107c6fe834e64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -355,9 +355,7 @@
       <x:c r="I1" t="str">
         <x:v>targetPolicy</x:v>
       </x:c>
-      <x:c r="J1" t="str">
-        <x:v>status</x:v>
-      </x:c>
+      <x:c r="J1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -387,25 +385,37 @@
       <x:c r="I2" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>string?</x:v>
-      </x:c>
+      <x:c r="J2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3"/>
-      <x:c r="E3"/>
-      <x:c r="F3"/>
-      <x:c r="G3"/>
-      <x:c r="H3"/>
-      <x:c r="I3"/>
-      <x:c r="J3" t="str">
-        <x:v>状态标注(CORE_COMPLETE)</x:v>
-      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>主键，兵种唯一 ID</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>显示名</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>动画键，关联 soldier_visual 表取得锚点偏移（knife/bow/pike/cavalry）</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>攻击范围，以格为单位</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>基础攻击力</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>攻击间隔，秒</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>伤害模式：近战/单体/近战枪击/范围</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>选敌策略：nearest（最近）/ closest_end（离终点最近）</x:v>
+      </x:c>
+      <x:c r="J3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -425,30 +435,14 @@
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>显示名</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>动画键</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>攻击距离(格)</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>攻击力</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>攻击间隔(秒)</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>伤害模式</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>目标策略</x:v>
-      </x:c>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
       <x:c r="J5"/>
     </x:row>
     <x:row r="6">
@@ -477,9 +471,7 @@
       <x:c r="I6" t="str">
         <x:v>nearest</x:v>
       </x:c>
-      <x:c r="J6" t="str">
-        <x:v>CORE_COMPLETE</x:v>
-      </x:c>
+      <x:c r="J6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -507,9 +499,7 @@
       <x:c r="I7" t="str">
         <x:v>closest_end</x:v>
       </x:c>
-      <x:c r="J7" t="str">
-        <x:v>CORE_COMPLETE</x:v>
-      </x:c>
+      <x:c r="J7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -537,9 +527,7 @@
       <x:c r="I8" t="str">
         <x:v>nearest</x:v>
       </x:c>
-      <x:c r="J8" t="str">
-        <x:v>CORE_COMPLETE</x:v>
-      </x:c>
+      <x:c r="J8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -567,9 +555,7 @@
       <x:c r="I9" t="str">
         <x:v>nearest</x:v>
       </x:c>
-      <x:c r="J9" t="str">
-        <x:v>CORE_COMPLETE</x:v>
-      </x:c>
+      <x:c r="J9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
